--- a/templates/eudamed_master_data_demo.xlsx
+++ b/templates/eudamed_master_data_demo.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -437,15 +437,8 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,47 +474,12 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>animal_tissues_cells</t>
+          <t>active</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>human_tissues_cells</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>human_product_check</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>medicinal_product_check</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>administering_medicine</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>implantable</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
           <t>measuring_function</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>reusable</t>
         </is>
       </c>
     </row>
@@ -566,41 +524,6 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -635,52 +558,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="5">
     <dataValidation sqref="B2:B201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"EUDAMED,GS1,HIBCC,ICCBBA,IFA"</formula1>
     </dataValidation>
@@ -694,27 +582,6 @@
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="I2:I201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="L2:L201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M2:M201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates/eudamed_master_data_demo.xlsx
+++ b/templates/eudamed_master_data_demo.xlsx
@@ -595,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -603,16 +603,9 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -643,50 +636,15 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>sterile</t>
+          <t>intended_purpose</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>sterilization</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>number_of_reuses</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>base_quantity</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>latex</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>reprocessed</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>intended_purpose</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>single_use</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
           <t>software_version</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>direct_marking_di</t>
         </is>
@@ -720,38 +678,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
           <t>Gravity infusion of standard infusion solutions</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -783,38 +710,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
           <t>Gravity infusion of standard infusion solutions, bulk pack</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -846,63 +742,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>Continuous monitoring of vital signs in clinical settings</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Continuous monitoring of vital signs in clinical settings</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
           <t>2.4.1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="7">
+  <dataValidations count="2">
     <dataValidation sqref="B2:B201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"EUDAMED,GS1,HIBCC,ICCBBA,IFA"</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"ON_THE_MARKET,NOT_INTENDED_FOR_EU_MARKET,NO_LONGER_PLACED_ON_THE_MARKET"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M2:M201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1112,7 +967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1139,65 +994,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BATCH_NUMBER</t>
+          <t>MANUFACTURING_DATE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>04012345000012</t>
+          <t>04012345000029</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EXPIRATION_DATE</t>
+          <t>MANUFACTURING_DATE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>04012345000029</t>
+          <t>04012345000036</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BATCH_NUMBER</t>
+          <t>SERIALISATION_NUMBER</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>04012345000029</t>
+          <t>04012345000036</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
-        <is>
-          <t>EXPIRATION_DATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>04012345000036</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SERIALISATION_NUMBER</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>04012345000036</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
         <is>
           <t>SOFTWARE_IDENTIFICATION</t>
         </is>
@@ -1206,7 +1037,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
-      <formula1>"BATCH_NUMBER,SERIALISATION_NUMBER,MANUFACTURING_DATE,EXPIRATION_DATE,SOFTWARE_IDENTIFICATION"</formula1>
+      <formula1>"SERIALISATION_NUMBER,MANUFACTURING_DATE,SOFTWARE_IDENTIFICATION"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/templates/eudamed_master_data_demo.xlsx
+++ b/templates/eudamed_master_data_demo.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -437,8 +437,9 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,10 +475,15 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
+          <t>special_device</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
           <t>active</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>measuring_function</t>
         </is>
@@ -514,12 +520,12 @@
           <t>DEVICE</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
@@ -558,17 +564,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>MDR_SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="B2:B201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"EUDAMED,GS1,HIBCC,ICCBBA,IFA"</formula1>
     </dataValidation>
@@ -579,9 +590,12 @@
       <formula1>"DEVICE,SYSTEM,PROCEDURE_PACK"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"MDR_SOFTWARE,MDR_STANDARD_SOFT_CONTACT_LENSES,MDR_RIGID_GAS_PERMEABLE,MDR_MADE_TO_ORDER,MDR_SPECTACLES_FRAMES,MDR_SPECTACLES_LENSES,MDR_READY_MADE_SPECTACLES,MDR_ORTHOPEDIC,MDR_MADE_TO_ORDER_RIGID_GAS_PERMEABLE,MDD_SOFTWARE,MDD_STANDARD_SOFT_CONTACT_LENSES,MDD_RIGID_GAS_PERMEABLE,MDD_MADE_TO_ORDER,MDD_SPECTACLES_FRAMES,MDD_SPECTACLES_LENSES,MDD_READY_MADE_SPECTACLES,MDD_ORTHOPEDIC,AIMDD_SOFTWARE,AIMDD_ORTHOPEDIC"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
